--- a/uploads/group_output.xlsx
+++ b/uploads/group_output.xlsx
@@ -477,21 +477,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Neha</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -503,17 +503,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -529,21 +529,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Manish</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -555,21 +555,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Preeti</t>
+          <t>Amit</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -581,21 +581,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yash</t>
+          <t>Mohit</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -633,69 +633,69 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Palak</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Group 1</t>
+          <t>Group 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Abhishek</t>
+          <t>Simran</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Group 1</t>
+          <t>Group 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Meena</t>
+          <t>Bhavna</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -704,28 +704,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Group 1</t>
+          <t>Group 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Palak</t>
+          <t>Sumit</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -737,21 +737,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nandini</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -763,21 +763,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shruti</t>
+          <t>Abhishek</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -789,17 +789,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nikhil</t>
+          <t>Varun</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -815,17 +815,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pooja</t>
+          <t>Ananya</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -834,128 +834,128 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amit</t>
+          <t>Shruti</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rajat</t>
+          <t>Payal</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Tanvi</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Yash</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sahil</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -964,28 +964,28 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Group 2</t>
+          <t>Group 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ananya</t>
+          <t>Karan</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shreya</t>
+          <t>Isha</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1016,24 +1016,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Simran</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
@@ -1068,24 +1068,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Gaurav</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1094,24 +1094,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Manish</t>
+          <t>Rajat</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1120,24 +1120,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Harsh</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aditya</t>
+          <t>Hemant</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1172,50 +1172,50 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mohit</t>
+          <t>Sakshi</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Muskan</t>
+          <t>Neha</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1224,50 +1224,50 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Group 3</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Isha</t>
+          <t>Nikhil</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D32" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Komal</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Harsh</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>10</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1302,50 +1302,50 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Payal</t>
+          <t>Aditya</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D35" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Komal</t>
+          <t>Ritika</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1354,102 +1354,102 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sumit</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deepak</t>
+          <t>Nandini</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ritesh</t>
+          <t>Tanya</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D39" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>Rahul</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>10</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1458,76 +1458,76 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ritika</t>
+          <t>Deepak</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>10</v>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D41" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Group 4</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sakshi</t>
+          <t>Ritesh</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>10</v>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Muskan</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>10</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1536,24 +1536,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>10</v>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1562,24 +1562,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bhavna</t>
+          <t>Shreya</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D45" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1588,50 +1588,50 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gaurav</t>
+          <t>Preeti</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D46" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tanvi</t>
+          <t>Pooja</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
@@ -1692,24 +1692,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Karan</t>
+          <t>Sahil</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>10</v>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1718,33 +1718,33 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hemant</t>
+          <t>Meena</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>10</v>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Group 5</t>
+          <t>Group 7</t>
         </is>
       </c>
     </row>
